--- a/output/pdf_financials_xlsx/JOY.xlsx
+++ b/output/pdf_financials_xlsx/JOY.xlsx
@@ -5871,16 +5871,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>-16.796</v>
+        <v>-15.203</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>-174.204</v>
+        <v>-173.623</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>-8.699</v>
+        <v>-6.117</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>8.786</v>
+        <v>12.015</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>-29.702</v>
@@ -5904,10 +5904,10 @@
         <v>-2.576</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.729</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.629</v>
       </c>
     </row>
     <row r="119">
@@ -15520,7 +15520,11 @@
           <t>Exploration and evaluation expenditures 7</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -26072,7 +26076,11 @@
           <t>Exploration and evaluation expense 7</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -28521,7 +28529,11 @@
           <t>Exploration and evaluation expense 9</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E280" s="5" t="n">
         <v>1.593</v>
       </c>

--- a/output/pdf_financials_xlsx/JOY.xlsx
+++ b/output/pdf_financials_xlsx/JOY.xlsx
@@ -823,37 +823,37 @@
         <v>288.291</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>3.485</v>
+        <v>259.207</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>4.988</v>
+        <v>0.716</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5.677</v>
+        <v>149.127</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8.513</v>
+        <v>113.201</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>9.276</v>
+        <v>115.735</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>129.911</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>16.068</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>138.993</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>166.963</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>159.428</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>143.968</v>
       </c>
     </row>
     <row r="11">
@@ -869,37 +869,37 @@
         <v>-115.307</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>102.413</v>
+        <v>-153.309</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>72.351</v>
+        <v>76.623</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>105.067</v>
+        <v>-38.383</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>86.245</v>
+        <v>-18.443</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>87.376</v>
+        <v>-19.083</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>72.31699999999999</v>
+        <v>-57.594</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>115.202</v>
+        <v>99.134</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>199.975</v>
+        <v>60.982</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>186.918</v>
+        <v>19.955</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>166.608</v>
+        <v>7.18</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>171.649</v>
+        <v>27.681</v>
       </c>
     </row>
     <row r="12">
@@ -1961,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.584</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>8.227</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
@@ -1973,22 +1973,22 @@
         <v>0</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>15.359</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>17.715</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>8.212999999999999</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.541</v>
       </c>
     </row>
     <row r="35">
@@ -2053,10 +2053,10 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.584</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>8.227</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -2065,22 +2065,22 @@
         <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>6.59</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>15.359</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>17.715</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>8.212999999999999</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.541</v>
       </c>
     </row>
     <row r="37">
@@ -2605,10 +2605,10 @@
         <v>5.952</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.198</v>
+        <v>1.614</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>11.854</v>
+        <v>3.627</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>3.087</v>
@@ -2617,22 +2617,22 @@
         <v>1.322</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>8.164999999999999</v>
+        <v>1.575</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>16.726</v>
+        <v>1.367</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>33.05</v>
+        <v>1.65</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>21.986</v>
+        <v>4.271</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>11.445</v>
+        <v>3.232</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>11.565</v>
+        <v>10.024</v>
       </c>
     </row>
     <row r="49">
@@ -6183,25 +6183,25 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-1.613</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-1.428</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.355</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.343</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.399</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.66</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.806</v>
       </c>
     </row>
     <row r="125">
@@ -6231,25 +6231,25 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-1.613</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-1.428</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.355</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.343</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.399</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.66</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.806</v>
       </c>
     </row>
     <row r="126">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15289,7 +15289,11 @@
           <t>Lease payments 12</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -17187,7 +17191,11 @@
           <t>Lease payments 13</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -24500,7 +24508,11 @@
           <t>Lease payments 11</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -31636,7 +31648,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -37604,7 +37616,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -37619,7 +37631,7 @@
         <v>259.207</v>
       </c>
       <c r="H397" s="5" t="n">
-        <v>-0.716</v>
+        <v>0.716</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/JOY.xlsx
+++ b/output/pdf_financials_xlsx/JOY.xlsx
@@ -5516,10 +5516,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>5.722</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>6.363</v>
       </c>
       <c r="M110" s="3" t="n">
         <v>0</v>
@@ -14418,7 +14418,11 @@
           <t>Deferred income tax expense 16</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -16553,7 +16557,11 @@
           <t>Deferred income tax expense 18</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -18204,7 +18212,11 @@
           <t>Accretion 16</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -18362,7 +18374,11 @@
           <t>Deferred income tax expense (recovery) 17</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -19944,7 +19960,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -22292,7 +22312,11 @@
           <t>Deferred tax expense (recovery) 17</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -23870,7 +23894,11 @@
           <t>Deferred tax expense 16</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -25863,7 +25891,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E246" s="5" t="n">
         <v>4.326</v>
       </c>
@@ -27512,7 +27544,11 @@
           <t>Deferred tax expense (recovery) 18</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -28462,7 +28498,11 @@
           <t>Deferred tax recovery 18</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -29740,7 +29780,11 @@
           <t>Deferred income tax expense (recovery) 18</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E295" s="5" t="n">
         <v>2.099</v>
       </c>
@@ -34406,7 +34450,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -35054,7 +35102,11 @@
           <t>Total income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E365" t="inlineStr">
         <is>
           <t>-</t>
@@ -39064,7 +39116,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
